--- a/Result/profitability/8472.xlsx
+++ b/Result/profitability/8472.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM51"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6895,6 +6895,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>8472</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>126</v>
+      </c>
+      <c r="D52" t="n">
+        <v>81</v>
+      </c>
+      <c r="E52" t="n">
+        <v>45</v>
+      </c>
+      <c r="F52" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-2.54%</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M52" t="n">
+        <v>-0.49125</v>
+      </c>
+      <c r="N52" t="n">
+        <v>44.33125</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W52" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.619999999999997</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.04795737122557719</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>4.229999999999997</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0.1357074109720884</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK52" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
